--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20232.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,51 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>CUAPIO</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>JURISEL</t>
-  </si>
-  <si>
-    <t>DANIEL DE JESUS</t>
-  </si>
-  <si>
-    <t>MICHEL LEONEL</t>
   </si>
 </sst>
 </file>
@@ -694,16 +649,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>56.67</v>
+      </c>
+      <c r="H2">
+        <v>6.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -717,16 +675,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>62.07</v>
+      </c>
+      <c r="H3">
+        <v>5.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -740,16 +701,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>78.26000000000001</v>
+      </c>
+      <c r="H4">
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -763,16 +727,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H5">
+        <v>6.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -786,16 +753,19 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H6">
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -851,16 +821,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>56.67</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -877,16 +847,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>48.28</v>
+        <v>62.07</v>
       </c>
       <c r="H3">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -903,16 +873,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>56.52</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -929,16 +899,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>87.88</v>
+        <v>66.67</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -964,7 +934,7 @@
         <v>71.43000000000001</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -974,7 +944,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1004,121 +974,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920199</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920222</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920281</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920285</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920299</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20232.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -80,6 +80,33 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TRISTAN YABAL</t>
+  </si>
+  <si>
+    <t>GISELA GUADALUPE</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
   </si>
 </sst>
 </file>
@@ -581,7 +608,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -590,13 +617,13 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -750,7 +777,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -759,13 +786,13 @@
         <v>4</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -821,16 +848,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>56.67</v>
+        <v>76.67</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -847,16 +874,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>62.07</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -873,16 +900,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>78.26000000000001</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -899,16 +926,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>66.67</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -919,22 +946,22 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>71.43000000000001</v>
+        <v>86.67</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -944,7 +971,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -974,6 +1001,75 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920196</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>23330051920328</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920135</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20232.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -82,13 +82,25 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>PERALTA</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>CRISTOBAL</t>
@@ -97,16 +109,19 @@
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>RIVERA</t>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
+    <t>ANGEL JESUS</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
   </si>
   <si>
     <t>TRISTAN YABAL</t>
   </si>
   <si>
     <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
-    <t>PEDRO ANGEL</t>
   </si>
 </sst>
 </file>
@@ -971,7 +986,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1003,16 +1018,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920196</v>
+        <v>23330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1026,16 +1041,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920328</v>
+        <v>23330051920216</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1055,10 +1070,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1068,6 +1083,52 @@
       </c>
       <c r="G4">
         <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920196</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>23330051920328</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20232.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -100,6 +103,9 @@
     <t>AUTRAN</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -110,6 +116,9 @@
   </si>
   <si>
     <t>AXEL AARON</t>
+  </si>
+  <si>
+    <t>FERNANDA YAMILET</t>
   </si>
   <si>
     <t>ANGEL JESUS</t>
@@ -986,7 +995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1024,10 +1033,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1041,22 +1050,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920216</v>
+        <v>23330051920271</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1064,22 +1073,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920135</v>
+        <v>23330051920216</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1087,47 +1096,70 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920196</v>
+        <v>21330051920135</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920328</v>
+        <v>22330051920196</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920328</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
         <v>13</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>1</v>
       </c>
     </row>
